--- a/sponsorship_form_templates/035_gilliganandtheskippertoo--sponsorship_form_templates.xlsx
+++ b/sponsorship_form_templates/035_gilliganandtheskippertoo--sponsorship_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>acupuncture</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Acupuncture</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>counseling</t>
+          <t>herbal_remedies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Counseling</t>
+          <t>Herbal Remedies</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>herbal_remedies</t>
+          <t>hypnosis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Herbal Remedies</t>
+          <t>Hypnosis</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hypnosis</t>
+          <t>mindfulness_and_meditation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hypnosis</t>
+          <t>Mindfulness and Meditation</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mindfulness_and_meditation</t>
+          <t>narcotic_anonymous_meetings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mindfulness and Meditation</t>
+          <t>Narcotic Anonymous Meetings</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>narcotic_anonymous_meetings</t>
+          <t>nicotine_gum_or_lozenges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Narcotic Anonymous Meetings</t>
+          <t>Nicotine gum or lozenges</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quit_smoking_methods_choices</t>
+          <t>support_system_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nicotine_gum_or_lozenges</t>
+          <t>family_support</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nicotine gum or lozenges</t>
+          <t>Family Support</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>family_support</t>
+          <t>online_support_groups</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Family Support</t>
+          <t>Online Support Groups</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>online_support_groups</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Online Support Groups</t>
+          <t>Social Services</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>trusted_friends</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Social Services</t>
+          <t>Trusted Friends</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trusted_friends</t>
+          <t>trusted_therapist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trusted Friends</t>
+          <t>Trusted Therapist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>support_system_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trusted_therapist</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trusted Therapist</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>asthma</t>
+          <t>bronchitis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Asthma</t>
+          <t>Bronchitis</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bronchitis</t>
+          <t>breathing_difficulty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bronchitis</t>
+          <t>Breathing Difficulty</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>breathing_difficulty</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Breathing Difficulty</t>
+          <t>Chest Pain</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>coughing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chest Pain</t>
+          <t>Coughing</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>coughing</t>
+          <t>emphysema</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coughing</t>
+          <t>Emphysema</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>emphysema</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emphysema</t>
+          <t>Heart Disease</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>kidney_disease</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Heart Disease</t>
+          <t>Kidney Disease</t>
         </is>
       </c>
     </row>
@@ -1488,27 +1488,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kidney_disease</t>
+          <t>pulmonary_fibrosis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Kidney Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>medical_condition_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pulmonary_fibrosis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Pulmonary Fibrosis</t>
         </is>
